--- a/attendance_config.xlsx
+++ b/attendance_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AttendanceSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A468EB-3212-4E22-8A44-3E8DF566ADB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918EF49C-06F5-4CA2-B651-E51623D360AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F772F950-EDB8-4EC7-B9CD-482C4AEEAD6A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F772F950-EDB8-4EC7-B9CD-482C4AEEAD6A}"/>
   </bookViews>
   <sheets>
     <sheet name="EMPLOYEES" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="82">
   <si>
     <t>Employee Name</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Ahmad Jararah</t>
   </si>
   <si>
-    <t>Ahmed Refaat</t>
-  </si>
-  <si>
     <t>Aslam</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>Raed</t>
   </si>
   <si>
-    <t>Ramiz</t>
-  </si>
-  <si>
     <t>Umar Farooq</t>
   </si>
   <si>
@@ -207,9 +201,6 @@
     <t>ahmad jararah</t>
   </si>
   <si>
-    <t>ramiz ghassan</t>
-  </si>
-  <si>
     <t>umar farooq</t>
   </si>
   <si>
@@ -225,9 +216,6 @@
     <t>ibrahim tareq</t>
   </si>
   <si>
-    <t>ahmed refaat</t>
-  </si>
-  <si>
     <t>mohammad hamza</t>
   </si>
   <si>
@@ -270,13 +258,34 @@
     <t>hamza nahdi</t>
   </si>
   <si>
-    <t>accesscontroler.ddns.net:58081</t>
-  </si>
-  <si>
-    <t>accesscontroler.ddns.net:58082</t>
-  </si>
-  <si>
     <t>Remote Connection Link</t>
+  </si>
+  <si>
+    <t>spc.webredirect.org:58081</t>
+  </si>
+  <si>
+    <t>spc.webredirect.org:58082</t>
+  </si>
+  <si>
+    <t>Obada</t>
+  </si>
+  <si>
+    <t>Sanabil</t>
+  </si>
+  <si>
+    <t>obada</t>
+  </si>
+  <si>
+    <t>raed</t>
+  </si>
+  <si>
+    <t>sanabil</t>
+  </si>
+  <si>
+    <t>kishen</t>
+  </si>
+  <si>
+    <t>mohammed al-dosari</t>
   </si>
 </sst>
 </file>
@@ -306,7 +315,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,12 +325,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -338,11 +341,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -689,44 +691,44 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>22</v>
+      <c r="A2" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -734,273 +736,282 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2">
         <v>0.25</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>75</v>
+        <v>51</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>12</v>
+      <c r="A15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
+      <c r="D20" s="3" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>71</v>
-      </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C23" s="2">
-        <v>0.375</v>
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1023,53 +1034,53 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
